--- a/BIRK.xlsx
+++ b/BIRK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED565B9B-46AB-46E1-970A-B55D37A782FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B245F6-3168-436F-B04B-1982B526BC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{18F8973A-4B1D-45B3-BBD1-81233DF5C159}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{18F8973A-4B1D-45B3-BBD1-81233DF5C159}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -250,13 +250,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -339,29 +345,29 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -721,7 +727,7 @@
         <v>55</v>
       </c>
       <c r="I2" s="2">
-        <v>34.32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -730,7 +736,7 @@
       </c>
       <c r="I3" s="11">
         <f>+I2*I10</f>
-        <v>29.172000000000001</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -741,7 +747,7 @@
         <v>183.90605600000001</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -753,7 +759,7 @@
       </c>
       <c r="I5" s="3">
         <f>+I3*I4</f>
-        <v>5364.9074656319999</v>
+        <v>6409.1260516000002</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -764,10 +770,10 @@
         <v>22</v>
       </c>
       <c r="I6" s="3">
-        <v>201.46700000000001</v>
+        <v>693.63499999999999</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -775,11 +781,11 @@
         <v>23</v>
       </c>
       <c r="I7" s="3">
-        <f>1131.758+16.91</f>
-        <v>1148.6680000000001</v>
+        <f>1678.284+9.126</f>
+        <v>1687.41</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -788,7 +794,7 @@
       </c>
       <c r="I8" s="3">
         <f>+I5-I6+I7</f>
-        <v>6312.1084656319999</v>
+        <v>7402.9010515999998</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -961,7 +967,9 @@
       <c r="L3" s="3">
         <v>471.67</v>
       </c>
-      <c r="M3" s="3"/>
+      <c r="M3" s="3">
+        <v>441.68900000000002</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -1045,7 +1053,9 @@
       <c r="L4" s="3">
         <v>146.381</v>
       </c>
-      <c r="M4" s="3"/>
+      <c r="M4" s="3">
+        <v>277.70699999999999</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -1129,7 +1139,9 @@
       <c r="L5" s="3">
         <v>324.35899999999998</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="3">
+        <v>347.43400000000003</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -1213,7 +1225,9 @@
       <c r="L6" s="3">
         <v>235.131</v>
       </c>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3">
+        <v>297.21699999999998</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -1297,7 +1311,9 @@
       <c r="L7" s="3">
         <v>58.561</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3">
+        <v>74.745000000000005</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1381,7 +1397,9 @@
       <c r="L8" s="3">
         <v>0.28199999999999997</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3">
+        <v>0.13100000000000001</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -1465,7 +1483,9 @@
       <c r="L9" s="7">
         <v>618.33299999999997</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="7">
+        <v>719.52700000000004</v>
+      </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7">
@@ -1565,7 +1585,9 @@
       <c r="L10" s="3">
         <v>284.77999999999997</v>
       </c>
-      <c r="M10" s="3"/>
+      <c r="M10" s="3">
+        <v>294.62599999999998</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1618,7 +1640,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C11:L11" si="3">+C9-C10</f>
+        <f t="shared" ref="C11:M11" si="3">+C9-C10</f>
         <v>184.86799999999999</v>
       </c>
       <c r="D11" s="3">
@@ -1657,7 +1679,10 @@
         <f t="shared" si="3"/>
         <v>333.553</v>
       </c>
-      <c r="M11" s="3"/>
+      <c r="M11" s="3">
+        <f t="shared" si="3"/>
+        <v>424.90100000000007</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3">
@@ -1757,7 +1782,9 @@
       <c r="L12" s="3">
         <v>138.31100000000001</v>
       </c>
-      <c r="M12" s="3"/>
+      <c r="M12" s="3">
+        <v>186.00800000000001</v>
+      </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1841,7 +1868,9 @@
       <c r="L13" s="3">
         <v>32.973999999999997</v>
       </c>
-      <c r="M13" s="3"/>
+      <c r="M13" s="3">
+        <v>32.518000000000001</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -1925,7 +1954,9 @@
       <c r="L14" s="3">
         <v>6.9530000000000003</v>
       </c>
-      <c r="M14" s="3"/>
+      <c r="M14" s="3">
+        <v>3.52</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -2009,7 +2040,9 @@
       <c r="L15" s="3">
         <v>0.13500000000000001</v>
       </c>
-      <c r="M15" s="3"/>
+      <c r="M15" s="3">
+        <v>0.19600000000000001</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -2062,7 +2095,7 @@
         <v>38</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:L16" si="6">+C11-SUM(C12:C14)+C15</f>
+        <f t="shared" ref="C16:M16" si="6">+C11-SUM(C12:C14)+C15</f>
         <v>35.569999999999993</v>
       </c>
       <c r="D16" s="3">
@@ -2101,7 +2134,10 @@
         <f t="shared" si="6"/>
         <v>155.44999999999999</v>
       </c>
-      <c r="M16" s="3"/>
+      <c r="M16" s="3">
+        <f t="shared" si="6"/>
+        <v>203.05100000000004</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3">
@@ -2201,7 +2237,9 @@
       <c r="L17" s="3">
         <v>33.805</v>
       </c>
-      <c r="M17" s="3"/>
+      <c r="M17" s="3">
+        <v>43.009</v>
+      </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -2254,7 +2292,7 @@
         <v>40</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" ref="C18:L18" si="9">+C16-C17</f>
+        <f t="shared" ref="C18:M18" si="9">+C16-C17</f>
         <v>-0.48000000000000398</v>
       </c>
       <c r="D18" s="3">
@@ -2293,7 +2331,10 @@
         <f t="shared" si="9"/>
         <v>121.64499999999998</v>
       </c>
-      <c r="M18" s="3"/>
+      <c r="M18" s="3">
+        <f t="shared" si="9"/>
+        <v>160.04200000000003</v>
+      </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3">
@@ -2393,7 +2434,9 @@
       <c r="L19" s="3">
         <v>39.762</v>
       </c>
-      <c r="M19" s="3"/>
+      <c r="M19" s="3">
+        <v>50.459000000000003</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -2446,7 +2489,7 @@
         <v>42</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:L20" si="13">+C18-C19</f>
+        <f t="shared" ref="C20:M20" si="13">+C18-C19</f>
         <v>-7.1540000000000044</v>
       </c>
       <c r="D20" s="3">
@@ -2485,7 +2528,10 @@
         <f t="shared" si="13"/>
         <v>81.882999999999981</v>
       </c>
-      <c r="M20" s="3"/>
+      <c r="M20" s="3">
+        <f t="shared" si="13"/>
+        <v>109.58300000000003</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3">
@@ -2605,7 +2651,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" ref="C22:L22" si="16">+C20/C23</f>
+        <f t="shared" ref="C22:M22" si="16">+C20/C23</f>
         <v>-3.8273026460271399E-2</v>
       </c>
       <c r="D22" s="8">
@@ -2644,7 +2690,10 @@
         <f t="shared" si="16"/>
         <v>0.44524363025870112</v>
       </c>
-      <c r="M22" s="8"/>
+      <c r="M22" s="8">
+        <f t="shared" si="16"/>
+        <v>0.59586401004652079</v>
+      </c>
       <c r="N22" s="8"/>
       <c r="O22" s="3"/>
       <c r="P22" s="8" t="e">
@@ -2743,7 +2792,9 @@
       <c r="L23" s="3">
         <v>183.90605600000001</v>
       </c>
-      <c r="M23" s="3"/>
+      <c r="M23" s="3">
+        <v>183.90605600000001</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -2855,7 +2906,7 @@
         <v>0.16118223451802938</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:L27" si="18">+H5/D5-1</f>
+        <f t="shared" ref="H25:M27" si="18">+H5/D5-1</f>
         <v>0.23018665910898028</v>
       </c>
       <c r="I25" s="9">
@@ -2874,7 +2925,10 @@
         <f t="shared" si="18"/>
         <v>3.7869091653760956E-2</v>
       </c>
-      <c r="M25" s="9"/>
+      <c r="M25" s="9">
+        <f t="shared" si="18"/>
+        <v>0.11262193130215903</v>
+      </c>
       <c r="N25" s="9"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -2967,7 +3021,10 @@
         <f t="shared" si="18"/>
         <v>0.10470530198031436</v>
       </c>
-      <c r="M26" s="9"/>
+      <c r="M26" s="9">
+        <f t="shared" si="18"/>
+        <v>0.14931767999597834</v>
+      </c>
       <c r="N26" s="9"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -3060,7 +3117,10 @@
         <f t="shared" si="18"/>
         <v>0.2246131325805103</v>
       </c>
-      <c r="M27" s="9"/>
+      <c r="M27" s="9">
+        <f t="shared" si="18"/>
+        <v>0.18308588432682282</v>
+      </c>
       <c r="N27" s="9"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -3130,59 +3190,62 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="10">
-        <f>+G9/C9-1</f>
+        <f t="shared" ref="G28:M28" si="22">+G9/C9-1</f>
         <v>0.19409158732883491</v>
       </c>
       <c r="H28" s="10">
-        <f>+H9/D9-1</f>
+        <f t="shared" si="22"/>
         <v>0.19342786611365548</v>
       </c>
       <c r="I28" s="10">
-        <f>+I9/E9-1</f>
+        <f t="shared" si="22"/>
         <v>0.12444976432383426</v>
       </c>
       <c r="J28" s="10">
-        <f>+J9/F9-1</f>
+        <f t="shared" si="22"/>
         <v>0.1548476843278539</v>
       </c>
       <c r="K28" s="10">
-        <f>+K9/G9-1</f>
+        <f t="shared" si="22"/>
         <v>0.1110889944957274</v>
       </c>
       <c r="L28" s="10">
-        <f>+L9/H9-1</f>
+        <f t="shared" si="22"/>
         <v>7.6616231086657383E-2</v>
       </c>
-      <c r="M28" s="10"/>
+      <c r="M28" s="10">
+        <f t="shared" si="22"/>
+        <v>0.13303844470129533</v>
+      </c>
       <c r="N28" s="10"/>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="10" t="e">
-        <f t="shared" ref="Q28:W28" si="22">+Q9/P9-1</f>
+        <f t="shared" ref="Q28:W28" si="23">+Q9/P9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R28" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S28" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T28" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.20041147925747071</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.20964990538979866</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.16221013027168119</v>
       </c>
       <c r="X28" s="3"/>
@@ -3219,78 +3282,81 @@
         <v>49</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="23">+C11/C9</f>
+        <f t="shared" ref="C29:F29" si="24">+C11/C9</f>
         <v>0.61027848569278109</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.56345637556000705</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.59481229128228386</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.58961216770082747</v>
       </c>
       <c r="G29" s="9">
-        <f>+G11/G9</f>
+        <f t="shared" ref="G29:L29" si="25">+G11/G9</f>
         <v>0.60277176482297035</v>
       </c>
       <c r="H29" s="9">
-        <f>+H11/H9</f>
+        <f t="shared" si="25"/>
         <v>0.57732314174777577</v>
       </c>
       <c r="I29" s="9">
-        <f>+I11/I9</f>
+        <f t="shared" si="25"/>
         <v>0.60480724109586459</v>
       </c>
       <c r="J29" s="9">
-        <f>+J11/J9</f>
+        <f t="shared" si="25"/>
         <v>0.58141346435180441</v>
       </c>
       <c r="K29" s="9">
-        <f>+K11/K9</f>
+        <f t="shared" si="25"/>
         <v>0.55721544058004191</v>
       </c>
       <c r="L29" s="9">
-        <f>+L11/L9</f>
+        <f t="shared" si="25"/>
         <v>0.53943910481892443</v>
       </c>
-      <c r="M29" s="9"/>
+      <c r="M29" s="9">
+        <f t="shared" ref="M29" si="26">+M11/M9</f>
+        <v>0.59052822201251665</v>
+      </c>
       <c r="N29" s="9"/>
       <c r="O29" s="3"/>
       <c r="P29" s="9" t="e">
-        <f t="shared" ref="P29:W29" si="24">+P11/P9</f>
+        <f t="shared" ref="P29:W29" si="27">+P11/P9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q29" s="9" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R29" s="9" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S29" s="9" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.60330068480640597</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.62054170791689311</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.58773362738198787</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.59105981656590045</v>
       </c>
       <c r="X29" s="3"/>
@@ -3327,78 +3393,81 @@
         <v>50</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:F30" si="25">+C16/C9</f>
+        <f t="shared" ref="C30:F30" si="28">+C16/C9</f>
         <v>0.11742219170485005</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.27535096541463377</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.27529136373455537</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.21398794112742545</v>
       </c>
       <c r="G30" s="9">
-        <f>+G16/G9</f>
+        <f t="shared" ref="G30:L30" si="29">+G16/G9</f>
         <v>0.177015860377807</v>
       </c>
       <c r="H30" s="9">
-        <f>+H16/H9</f>
+        <f t="shared" si="29"/>
         <v>0.30526526561384582</v>
       </c>
       <c r="I30" s="9">
-        <f>+I16/I9</f>
+        <f t="shared" si="29"/>
         <v>0.31176048198386885</v>
       </c>
       <c r="J30" s="9">
-        <f>+J16/J9</f>
+        <f t="shared" si="29"/>
         <v>0.21319000338185717</v>
       </c>
       <c r="K30" s="9">
-        <f>+K16/K9</f>
+        <f t="shared" si="29"/>
         <v>0.19490821145453366</v>
       </c>
       <c r="L30" s="9">
-        <f>+L16/L9</f>
+        <f t="shared" si="29"/>
         <v>0.25140175277722521</v>
       </c>
-      <c r="M30" s="9"/>
+      <c r="M30" s="9">
+        <f t="shared" ref="M30" si="30">+M16/M9</f>
+        <v>0.28220066793879872</v>
+      </c>
       <c r="N30" s="9"/>
       <c r="O30" s="3"/>
       <c r="P30" s="9" t="e">
-        <f t="shared" ref="P30:W30" si="26">+P16/P9</f>
+        <f t="shared" ref="P30:W30" si="31">+P16/P9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q30" s="9" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R30" s="9" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S30" s="9" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.29209636371097319</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.17473428374748889</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.23332649928796623</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0.26200839217918703</v>
       </c>
       <c r="X30" s="3"/>
@@ -3435,78 +3504,81 @@
         <v>51</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="27">+C19/C18</f>
+        <f t="shared" ref="C31:F31" si="32">+C19/C18</f>
         <v>-13.904166666666551</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.31839196362321864</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.3266648631588438</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.32986772317720037</v>
       </c>
       <c r="G31" s="9">
-        <f>+G19/G18</f>
+        <f t="shared" ref="G31:L31" si="33">+G19/G18</f>
         <v>0.48744013043921358</v>
       </c>
       <c r="H31" s="9">
-        <f>+H19/H18</f>
+        <f t="shared" si="33"/>
         <v>0.29789394232888683</v>
       </c>
       <c r="I31" s="9">
-        <f>+I19/I18</f>
+        <f t="shared" si="33"/>
         <v>0.28078406491576635</v>
       </c>
       <c r="J31" s="9">
-        <f>+J19/J18</f>
+        <f t="shared" si="33"/>
         <v>7.3723578519410499E-2</v>
       </c>
       <c r="K31" s="9">
-        <f>+K19/K18</f>
+        <f t="shared" si="33"/>
         <v>0.26923466069234664</v>
       </c>
       <c r="L31" s="9">
-        <f>+L19/L18</f>
+        <f t="shared" si="33"/>
         <v>0.32686916848205849</v>
       </c>
-      <c r="M31" s="9"/>
+      <c r="M31" s="9">
+        <f t="shared" ref="M31" si="34">+M19/M18</f>
+        <v>0.31528598742830005</v>
+      </c>
       <c r="N31" s="9"/>
       <c r="O31" s="3"/>
       <c r="P31" s="9" t="e">
-        <f t="shared" ref="P31:W31" si="28">+P19/P18</f>
+        <f t="shared" ref="P31:W31" si="35">+P19/P18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q31" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R31" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S31" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0.25312145742523673</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0.51174081691094186</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0.34780891953897825</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0.25884718498659509</v>
       </c>
       <c r="X31" s="3"/>
